--- a/public/templates/주간업무보고(원본).xlsx
+++ b/public/templates/주간업무보고(원본).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\서재형\Desktop\new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EB648B-ADA2-4D8C-A243-ACFF5032CA58}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F19E1-C94E-441A-9892-5361B7DAE2D2}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{42A0E73B-0B8C-46D4-A56F-2A39110D2689}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>주간업무보고</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -126,10 +126,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>차주계획</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>담당</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -167,6 +163,14 @@
   </si>
   <si>
     <t>□특이사항</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요보고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -297,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -537,6 +541,154 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -546,7 +698,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -595,6 +747,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -625,47 +813,47 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -994,37 +1182,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
       <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="38"/>
       <c r="E2" s="26"/>
       <c r="F2" s="26"/>
       <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="38"/>
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
@@ -1034,8 +1222,8 @@
       <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
       <c r="D4" s="38"/>
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
@@ -1045,8 +1233,8 @@
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="39"/>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
@@ -1056,19 +1244,19 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1080,420 +1268,447 @@
       <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="E7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
-      <c r="E8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="J8" s="37"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="12"/>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48"/>
     </row>
     <row r="10" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="12"/>
-      <c r="E10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="48"/>
     </row>
     <row r="11" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="12"/>
-      <c r="E11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="12"/>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="48"/>
     </row>
     <row r="13" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="12"/>
-      <c r="E13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="12"/>
-      <c r="E14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
     </row>
     <row r="15" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="12"/>
-      <c r="E15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="48"/>
     </row>
     <row r="16" spans="1:10" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="12"/>
-      <c r="E16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="48"/>
     </row>
     <row r="17" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+    </row>
+    <row r="20" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+    </row>
+    <row r="21" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+    </row>
+    <row r="22" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17"/>
+      <c r="B22" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31" t="s">
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-    </row>
-    <row r="19" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-    </row>
-    <row r="20" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-    </row>
-    <row r="21" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-    </row>
-    <row r="22" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30" t="s">
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+    </row>
+    <row r="23" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="17"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+    </row>
+    <row r="24" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+    </row>
+    <row r="25" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30" t="s">
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-    </row>
-    <row r="23" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-    </row>
-    <row r="24" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-    </row>
-    <row r="25" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-    </row>
-    <row r="26" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="31" t="s">
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+    </row>
+    <row r="28" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
+      <c r="B30" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31" t="s">
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-    </row>
-    <row r="27" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-    </row>
-    <row r="28" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-    </row>
-    <row r="29" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-    </row>
-    <row r="30" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="30" t="s">
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+    </row>
+    <row r="33" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30" t="s">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-    </row>
-    <row r="31" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-    </row>
-    <row r="32" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-    </row>
-    <row r="33" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-    </row>
-    <row r="34" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="31" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="19"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+    </row>
+    <row r="36" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="19"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="19"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31" t="s">
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-    </row>
-    <row r="35" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="35"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-    </row>
-    <row r="36" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="35"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-    </row>
-    <row r="37" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="35"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-    </row>
-    <row r="38" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
     </row>
     <row r="39" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
     </row>
     <row r="40" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
     </row>
     <row r="41" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
     </row>
     <row r="42" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
     </row>
     <row r="43" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="A7:A17"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="A38:A43"/>
+  <mergeCells count="77">
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E19:G19"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="B38:D38"/>
@@ -1510,51 +1725,11 @@
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="A7:A17"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="A38:A43"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
